--- a/laporan_padel_dki_jakarta_2026-09-28.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-28.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp224.000</t>
+          <t>Rp125.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp6.570.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.478.000</t>
+          <t>Rp8.753.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>68</v>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.080.000</t>
+          <t>Rp5.080.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>180</v>
       </c>
       <c r="D42" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.450.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>112</v>
       </c>
       <c r="D75" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>80</v>
       </c>
       <c r="D86" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp1.791.000</t>
+          <t>Rp2.189.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.891.004</t>
+          <t>Rp11.656.004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.740.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp947.000</t>
+          <t>Rp1.296.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>53</v>
       </c>
       <c r="D25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.486.000</t>
+          <t>Rp2.988.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.998.000</t>
+          <t>Rp4.598.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp29.100.000</t>
+          <t>Rp29.350.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.930.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.110.000</t>
+          <t>Rp3.935.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.150.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp4.430.000</t>
+          <t>Rp4.630.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>75</v>
       </c>
       <c r="D30" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.625.000</t>
+          <t>Rp4.275.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.840.000</t>
+          <t>Rp1.940.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-28.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.328.000</t>
+          <t>Rp5.056.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -940,28 +940,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stone Padel - Citra Garden City</t>
+          <t>Atlas Sport Center</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp200.000</t>
+          <t>Rp100.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -971,28 +971,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daily Court</t>
+          <t>Stone Padel - Citra Garden City</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.610.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp210.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1002,28 +1002,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>River Padel</t>
+          <t>Daily Court</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp3.610.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp100.000 - Rp210.000</t>
         </is>
       </c>
     </row>
@@ -1033,28 +1033,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KSC Racquet Club</t>
+          <t>River Padel</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp14.490.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp305.000</t>
+          <t>Rp150.000</t>
         </is>
       </c>
     </row>
@@ -1064,28 +1064,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anwa Racquet Privé (ex Anwa Tennis Club)</t>
+          <t>KSC Racquet Club</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp10.275.000</t>
+          <t>Rp14.490.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rp199.000 - Rp700.000</t>
+          <t>Rp150.000 - Rp305.000</t>
         </is>
       </c>
     </row>
@@ -1095,28 +1095,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Padel Spot</t>
+          <t>Anwa Racquet Privé (ex Anwa Tennis Club)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="D22" t="n">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp10.275.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp199.000 - Rp700.000</t>
         </is>
       </c>
     </row>
@@ -1126,23 +1126,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IPC Padel Club Kedoya</t>
+          <t>Padel Spot</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1157,28 +1157,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Badel Padel</t>
+          <t>IPC Padel Club Kedoya</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp295.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1188,28 +1188,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Base Padel</t>
+          <t>Badel Padel</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp625.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp40.000 - Rp225.000</t>
+          <t>Rp100.000 - Rp295.000</t>
         </is>
       </c>
     </row>
@@ -1219,28 +1219,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Patra Padel House</t>
+          <t>Base Padel</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp200.000</t>
+          <t>Rp40.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -1250,28 +1250,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Terra Padel Court</t>
+          <t>Patra Padel House</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp199.000</t>
+          <t>Rp125.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1281,28 +1281,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tinny Padel</t>
+          <t>Terra Padel Court</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp376.000</t>
+          <t>Rp198.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp188.000</t>
+          <t>Rp99.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -1312,28 +1312,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kobana Padel</t>
+          <t>Tinny Padel</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp376.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp240.000</t>
+          <t>Rp125.000 - Rp188.000</t>
         </is>
       </c>
     </row>
@@ -1343,28 +1343,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PADELGROUNDS - MERUYA</t>
+          <t>Kobana Padel</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.436.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp180.000</t>
+          <t>Rp200.000 - Rp240.000</t>
         </is>
       </c>
     </row>
@@ -1374,28 +1374,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Glass House Padel</t>
+          <t>PADELGROUNDS - MERUYA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.495.000</t>
+          <t>Rp1.796.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rp60.000 - Rp249.000</t>
+          <t>Rp70.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -1405,28 +1405,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sini Padel Court</t>
+          <t>Glass House Padel</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.514.000</t>
+          <t>Rp1.495.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rp98.000 - Rp200.000</t>
+          <t>Rp60.000 - Rp249.000</t>
         </is>
       </c>
     </row>
@@ -1436,28 +1436,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Xcite Padel</t>
+          <t>Sini Padel Court</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.385.000</t>
+          <t>Rp2.514.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp230.000</t>
+          <t>Rp98.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1467,28 +1467,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hobi Padel Meruya</t>
+          <t>Xcite Padel</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.184.000</t>
+          <t>Rp3.385.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rp98.000 - Rp148.000</t>
+          <t>Rp125.000 - Rp230.000</t>
         </is>
       </c>
     </row>
@@ -1498,28 +1498,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Padel Point</t>
+          <t>Hobi Padel Meruya</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.184.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp98.000 - Rp148.000</t>
         </is>
       </c>
     </row>
@@ -1529,28 +1529,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RacketGo Citra 5</t>
+          <t>The Padel Point</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp190.000</t>
+          <t>Rp150.000</t>
         </is>
       </c>
     </row>
@@ -1560,28 +1560,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Eagle Padel PIK</t>
+          <t>RacketGo Citra 5</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.080.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rp170.000 - Rp250.000</t>
+          <t>Rp125.000 - Rp190.000</t>
         </is>
       </c>
     </row>
@@ -1591,28 +1591,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>La Chiquita Padel</t>
+          <t>Eagle Padel PIK</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp5.080.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp300.000</t>
+          <t>Rp170.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Padre Padel Duri Kosambi</t>
+          <t>La Chiquita Padel</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp210.000</t>
+          <t>Rp200.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -1653,14 +1653,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Padeloo</t>
+          <t>Padre Padel Duri Kosambi</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp978.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp195.000</t>
+          <t>Rp150.000 - Rp210.000</t>
         </is>
       </c>
     </row>
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CPH Citra Padel House</t>
+          <t>Padeloo</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.235.000</t>
+          <t>Rp978.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp170.000</t>
+          <t>Rp99.000 - Rp195.000</t>
         </is>
       </c>
     </row>
@@ -1715,28 +1715,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vamos Arena Indonesia</t>
+          <t>CPH Citra Padel House</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>159</v>
+        <v>32</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp400.000</t>
+          <t>Rp75.000 - Rp170.000</t>
         </is>
       </c>
     </row>
@@ -1746,28 +1746,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Level 9 Padel</t>
+          <t>Vamos Arena Indonesia</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp9.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp150.000</t>
+          <t>Rp200.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -1777,28 +1777,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Como Padel Court</t>
+          <t>The Level 9 Padel</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="D44" t="n">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.899.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp200.000</t>
+          <t>Rp125.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -1808,28 +1808,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>World Padel</t>
+          <t>Como Padel Court</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.899.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp225.000</t>
+          <t>Rp99.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1839,28 +1839,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Padelin</t>
+          <t>World Padel</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp580.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp200.000</t>
+          <t>Rp50.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -1870,28 +1870,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nordic Courts</t>
+          <t>Padelin</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.467.000</t>
+          <t>Rp580.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rp77.000 - Rp250.000</t>
+          <t>Rp70.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1901,28 +1901,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Courtyard Padel Club</t>
+          <t>Nordic Courts</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.685.000</t>
+          <t>Rp3.497.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rp165.000 - Rp650.000</t>
+          <t>Rp77.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -1932,28 +1932,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Padel On Mars</t>
+          <t>Courtyard Padel Club</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp2.685.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rp115.000 - Rp135.000</t>
+          <t>Rp165.000 - Rp650.000</t>
         </is>
       </c>
     </row>
@@ -1963,28 +1963,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Padel Meruya Airdome</t>
+          <t>Padel On Mars</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="D50" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp270.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp349.000 - Rp550.000</t>
+          <t>Rp115.000 - Rp135.000</t>
         </is>
       </c>
     </row>
@@ -1994,28 +1994,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hachi Padel Puri Indah Jakarta</t>
+          <t>Padel Meruya Airdome</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D51" t="n">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.896.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rp288.000</t>
+          <t>Rp349.000 - Rp550.000</t>
         </is>
       </c>
     </row>
@@ -2025,28 +2025,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JC Padel Kedoya</t>
+          <t>Hachi Padel Puri Indah Jakarta</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp4.896.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp198.000</t>
+          <t>Rp288.000</t>
         </is>
       </c>
     </row>
@@ -2056,28 +2056,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tennis Padel Matic Mal Ciputra</t>
+          <t>JC Padel Kedoya</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D53" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rp80.000</t>
+          <t>Rp99.000 - Rp198.000</t>
         </is>
       </c>
     </row>
@@ -2087,28 +2087,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Paddle Padel</t>
+          <t>Tennis Padel Matic Mal Ciputra</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp80.000</t>
         </is>
       </c>
     </row>
@@ -2118,28 +2118,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Roots Padel House</t>
+          <t>Paddle Padel</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp447.000</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rp149.000 - Rp200.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2149,28 +2149,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Coco Padel Court Jakarta</t>
+          <t>Roots Padel House</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rp90.000 - Rp180.000</t>
+          <t>Rp149.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2180,28 +2180,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zplay Padel</t>
+          <t>Coco Padel Court Jakarta</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp815.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rp65.000 - Rp175.000</t>
+          <t>Rp90.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -2211,28 +2211,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PPC - Puri Padel Club</t>
+          <t>Zplay Padel</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp815.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rp225.000 - Rp275.000</t>
+          <t>Rp65.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -2242,28 +2242,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Donkey Padel</t>
+          <t>PPC - Puri Padel Club</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp149.000</t>
+          <t>Rp225.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -2273,28 +2273,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sunrise Padel - Sunrise Garden</t>
+          <t>Donkey Padel</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp120.000</t>
+          <t>Rp99.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -2304,28 +2304,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ace Padel Club (APC) - Jalan Panjang Kedoya</t>
+          <t>Sunrise Padel - Sunrise Garden</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp10.480.000</t>
+          <t>Rp2.020.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp300.000</t>
+          <t>Rp100.000 - Rp120.000</t>
         </is>
       </c>
     </row>
@@ -2335,28 +2335,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Padel Quarter</t>
+          <t>Ace Padel Club (APC) - Jalan Panjang Kedoya</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.630.000</t>
+          <t>Rp10.480.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp380.000</t>
+          <t>Rp100.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -2366,28 +2366,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZEN PADEL</t>
+          <t>Padel Quarter</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.630.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp68.000 - Rp99.000</t>
+          <t>Rp80.000 - Rp380.000</t>
         </is>
       </c>
     </row>
@@ -2397,28 +2397,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Go 2 Padel</t>
+          <t>ZEN PADEL</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D64" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rp60.000 - Rp150.000</t>
+          <t>Rp59.000 - Rp68.000</t>
         </is>
       </c>
     </row>
@@ -2428,28 +2428,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YOLO Padel and Lifestyle Slipi</t>
+          <t>Go 2 Padel</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp275.000</t>
+          <t>Rp60.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -2459,28 +2459,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KALMA Social Club - Jl. Panjang, Kedoya</t>
+          <t>YOLO Padel and Lifestyle Slipi</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="D66" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp8.772.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp399.000</t>
+          <t>Rp200.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -2490,28 +2490,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Padel V</t>
+          <t>KALMA Social Club - Jl. Panjang, Kedoya</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp5.879.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rp160.000 - Rp260.000</t>
+          <t>Rp150.000 - Rp399.000</t>
         </is>
       </c>
     </row>
@@ -2521,28 +2521,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Country Club | Padel &amp; Lounge</t>
+          <t>Padel V</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D68" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp250.000</t>
+          <t>Rp160.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -2552,28 +2552,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Social Field</t>
+          <t>Country Club | Padel &amp; Lounge</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>176</v>
+        <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.839.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rp99.500 - Rp299.000</t>
+          <t>Rp200.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -2583,28 +2583,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PIPC - Play In Padel Collective - Srengseng</t>
+          <t>Social Field</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.919.000</t>
+          <t>Rp3.736.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp135.000</t>
+          <t>Rp99.500 - Rp299.000</t>
         </is>
       </c>
     </row>
@@ -2614,28 +2614,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>United Padel Club</t>
+          <t>PIPC - Play In Padel Collective - Srengseng</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="D71" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp4.117.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rp120.000 - Rp180.000</t>
+          <t>Rp99.000 - Rp135.000</t>
         </is>
       </c>
     </row>
@@ -2645,28 +2645,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Powerhouse Padel AZURE Taman Surya</t>
+          <t>United Padel Club</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp170.000</t>
+          <t>Rp120.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -2676,28 +2676,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kore Padel</t>
+          <t>Powerhouse Padel AZURE Taman Surya</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp325.000</t>
+          <t>Rp75.000 - Rp170.000</t>
         </is>
       </c>
     </row>
@@ -2707,28 +2707,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OLA PADEL CLUB</t>
+          <t>Kore Padel</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp4.565.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp260.000</t>
+          <t>Rp200.000 - Rp325.000</t>
         </is>
       </c>
     </row>
@@ -2738,28 +2738,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MMT Padel</t>
+          <t>OLA PADEL CLUB</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp315.000</t>
+          <t>Rp100.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -2769,28 +2769,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Clubhouse Meruya</t>
+          <t>MMT Padel</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D76" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp6.120.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp180.000</t>
+          <t>Rp100.000 - Rp315.000</t>
         </is>
       </c>
     </row>
@@ -2800,28 +2800,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Angke Padel</t>
+          <t>Clubhouse Meruya</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp6.480.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp150.000</t>
+          <t>Rp100.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -2831,28 +2831,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DAAN MOGOT PADEL COURT</t>
+          <t>Angke Padel</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp500.000</t>
+          <t>Rp50.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -2862,28 +2862,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kaia Padel Reserve</t>
+          <t>DAAN MOGOT PADEL COURT</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D79" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp200.000</t>
+          <t>Rp125.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -2893,28 +2893,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tangkas Padel</t>
+          <t>Kaia Padel Reserve</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="D80" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp300.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2924,28 +2924,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cosmo Padel</t>
+          <t>Tangkas Padel</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp275.000</t>
+          <t>Rp150.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -2955,14 +2955,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MAISON de PADEL</t>
+          <t>Cosmo Padel</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D82" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rp275.000 - Rp450.000</t>
+          <t>Rp100.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -2986,28 +2986,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Di Atas Social Club - Lippo Mall Puri</t>
+          <t>MAISON de PADEL</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="D83" t="n">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rp195.000 - Rp280.000</t>
+          <t>Rp275.000 - Rp450.000</t>
         </is>
       </c>
     </row>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Commune Courts</t>
+          <t>Di Atas Social Club - Lippo Mall Puri</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="D84" t="n">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp300.000</t>
+          <t>Rp195.000 - Rp280.000</t>
         </is>
       </c>
     </row>
@@ -3048,28 +3048,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EL WILLY PADEL</t>
+          <t>Commune Courts</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp380.000</t>
+          <t>Rp100.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -3079,28 +3079,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dash Padel House</t>
+          <t>EL WILLY PADEL</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="D86" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp2.189.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp249.000</t>
+          <t>Rp250.000 - Rp380.000</t>
         </is>
       </c>
     </row>
@@ -3110,28 +3110,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Citra Padel Club</t>
+          <t>Dash Padel House</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp2.388.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp225.000</t>
+          <t>Rp100.000 - Rp249.000</t>
         </is>
       </c>
     </row>
@@ -3141,28 +3141,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Malta Padel Club</t>
+          <t>Citra Padel Club</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp70.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -3172,28 +3172,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>De Luz Padel</t>
+          <t>Malta Padel Club</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.215.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp180.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -3203,28 +3203,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dale Padel</t>
+          <t>De Luz Padel</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="D90" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp50.000</t>
+          <t>Rp4.295.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp150.000</t>
+          <t>Rp80.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -3234,28 +3234,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nice Padel</t>
+          <t>Dale Padel</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp2.376.000</t>
+          <t>Rp50.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp50.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -3265,28 +3265,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Golcindo Padel Club</t>
+          <t>Nice Padel</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D92" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp804.000</t>
+          <t>Rp2.376.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rp59.000 - Rp149.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
     </row>
@@ -3296,28 +3296,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mono House</t>
+          <t>Golcindo Padel Club</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D93" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp804.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp225.000</t>
+          <t>Rp59.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -3327,28 +3327,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Seven Stars Arena</t>
+          <t>Mono House</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp3.330.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp220.000</t>
+          <t>Rp125.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -3358,28 +3358,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deuce Arena</t>
+          <t>Seven Stars Arena</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="D95" t="n">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp1.230.000</t>
+          <t>Rp3.330.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp250.000</t>
+          <t>Rp125.000 - Rp220.000</t>
         </is>
       </c>
     </row>
@@ -3389,28 +3389,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Alley Social Padel Mahjong By Homeground</t>
+          <t>Deuce Arena</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp575.000</t>
+          <t>Rp1.230.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp225.000</t>
+          <t>Rp70.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -3420,26 +3420,57 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>Alley Social Padel Mahjong By Homeground</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>68</v>
+      </c>
+      <c r="D97" t="n">
+        <v>65</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Rp575.000</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Rp75.000 - Rp225.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>SERA COMMUNITY CLUB</t>
         </is>
       </c>
-      <c r="C97" t="n">
+      <c r="C98" t="n">
         <v>28</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D98" t="n">
         <v>25</v>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>10.7%</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Rp730.000</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Rp165.000 - Rp400.000</t>
         </is>
@@ -3633,16 +3664,16 @@
         <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3788,16 +3819,16 @@
         <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp8.625.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3850,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3881,16 +3912,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4005,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp9.585.000</t>
+          <t>Rp7.605.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4129,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.296.000</t>
+          <t>Rp1.595.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4160,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4346,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp17.175.000</t>
+          <t>Rp17.725.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4439,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4594,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp378.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4687,16 +4718,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4811,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5059,16 +5090,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.075.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5338,16 +5369,16 @@
         <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp880.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5493,16 +5524,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5533,12 +5564,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.123.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rp270.000 - Rp297.000</t>
+          <t>Rp180.000 - Rp297.000</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5626,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5617,16 +5648,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5978,16 +6009,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6164,16 +6195,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.520.000</t>
+          <t>Rp4.970.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6226,16 +6257,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.150.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6319,16 +6350,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp3.390.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6463,16 +6494,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp8.080.000</t>
+          <t>Rp8.305.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6525,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp10.400.000</t>
+          <t>Rp10.595.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6556,16 +6587,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp6.625.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6649,16 +6680,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6680,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.714.000</t>
+          <t>Rp17.004.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6742,16 +6773,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.288.000</t>
+          <t>Rp4.567.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6773,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.325.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6925,24 +6956,24 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.033.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp538.000</t>
+          <t>Rp99.000 - Rp169.000</t>
         </is>
       </c>
     </row>
@@ -6959,16 +6990,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp198.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6990,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.400.000</t>
+          <t>Rp22.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7300,16 @@
         <v>75</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.275.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7331,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp9.825.000</t>
+          <t>Rp10.805.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7362,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.800.000</t>
+          <t>Rp11.325.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7517,16 +7548,16 @@
         <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7672,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.130.000</t>
+          <t>Rp9.530.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7734,16 +7765,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp410.000</t>
+          <t>Rp820.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7889,16 +7920,16 @@
         <v>48</v>
       </c>
       <c r="D50" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8002,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.940.000</t>
+          <t>Rp3.910.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8064,16 +8095,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp4.150.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8467,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.110.000</t>
+          <t>Rp4.410.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8498,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8529,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.308.000</t>
+          <t>Rp4.867.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8808,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9087,16 +9118,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.486.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9118,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.895.000</t>
+          <t>Rp6.095.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9211,16 +9242,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.194.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-28.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-28.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp7.580.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp270.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.329.986</t>
+          <t>Rp5.276.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.753.000</t>
+          <t>Rp9.688.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.150.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.610.000</t>
+          <t>Rp3.820.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,21 +1195,21 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp295.000</t>
+          <t>Rp100.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.514.000</t>
+          <t>Rp2.109.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.385.000</t>
+          <t>Rp3.775.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.184.000</t>
+          <t>Rp1.480.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp978.000</t>
+          <t>Rp1.758.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.400.000</t>
+          <t>Rp10.100.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>180</v>
       </c>
       <c r="D44" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.675.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.497.000</t>
+          <t>Rp3.893.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>84</v>
       </c>
       <c r="D51" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp798.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp248.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.020.000</t>
+          <t>Rp1.780.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp10.480.000</t>
+          <t>Rp9.980.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp1.630.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>32</v>
       </c>
       <c r="D66" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp5.879.000</t>
+          <t>Rp8.273.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>102</v>
       </c>
       <c r="D71" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp4.117.000</t>
+          <t>Rp4.252.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp4.180.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp6.480.000</t>
+          <t>Rp7.020.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>80</v>
       </c>
       <c r="D80" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>135</v>
       </c>
       <c r="D84" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.310.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.125.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3207,14 +3207,14 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp50.000</t>
+          <t>Rp280.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp1.230.000</t>
+          <t>Rp1.630.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>68</v>
       </c>
       <c r="D97" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp575.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp567.000</t>
+          <t>Rp729.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3571,21 +3571,21 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.656.004</t>
+          <t>Rp11.972.004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rp135.000 - Rp598.000</t>
+          <t>Rp135.000 - Rp570.000</t>
         </is>
       </c>
     </row>
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.720.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp7.605.000</t>
+          <t>Rp8.010.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.595.000</t>
+          <t>Rp1.944.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.988.000</t>
+          <t>Rp3.237.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp17.725.000</t>
+          <t>Rp17.975.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp1.299.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp378.000</t>
+          <t>Rp1.134.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp8.050.000</t>
+          <t>Rp10.750.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>77</v>
       </c>
       <c r="D46" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.075.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.968.000</t>
+          <t>Rp3.384.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp239.000</t>
+          <t>Rp496.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp3.123.000</t>
+          <t>Rp2.826.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp4.730.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp9.927.500</t>
+          <t>Rp10.367.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.270.000</t>
+          <t>Rp1.370.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp29.350.000</t>
+          <t>Rp30.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.970.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp4.630.000</t>
+          <t>Rp4.870.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp535.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp10.595.000</t>
+          <t>Rp10.790.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.625.000</t>
+          <t>Rp7.325.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.160.000</t>
+          <t>Rp8.632.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.004.000</t>
+          <t>Rp18.394.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.425.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp990.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.000.000</t>
+          <t>Rp23.600.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp8.650.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.699.000</t>
+          <t>Rp1.355.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp690.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>57</v>
       </c>
       <c r="D29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp6.970.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.205.000</t>
+          <t>Rp2.915.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.325.000</t>
+          <t>Rp11.925.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.496.000</t>
+          <t>Rp6.072.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp434.000</t>
+          <t>Rp1.574.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.625.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp19.550.000</t>
+          <t>Rp20.100.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.325.000</t>
+          <t>Rp6.725.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.910.000</t>
+          <t>Rp5.290.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp1.820.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp670.000</t>
+          <t>Rp855.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.560.000</t>
+          <t>Rp6.540.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.390.000</t>
+          <t>Rp5.590.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.574.999</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.580.000</t>
+          <t>Rp1.995.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.610.000</t>
+          <t>Rp1.805.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.259.000</t>
+          <t>Rp3.457.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp555.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.095.000</t>
+          <t>Rp5.545.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp713.000</t>
+          <t>Rp544.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-28.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-28.xlsx
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.276.987</t>
+          <t>Rp5.572.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.480.000</t>
+          <t>Rp1.676.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.310.000</t>
+          <t>Rp2.055.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.110.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.972.004</t>
+          <t>Rp12.292.006</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D34" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp4.730.000</t>
+          <t>Rp5.430.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp7.170.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp535.000</t>
+          <t>Rp1.041.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp23.600.000</t>
+          <t>Rp23.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.413.000</t>
+          <t>Rp5.612.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.925.000</t>
+          <t>Rp12.175.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp6.072.000</t>
+          <t>Rp6.260.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.290.000</t>
+          <t>Rp4.830.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.590.000</t>
+          <t>Rp5.790.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.486.000</t>
+          <t>Rp1.684.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.545.000</t>
+          <t>Rp5.745.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
